--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92561140618</v>
+        <v>46157.93066698194</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93066698194</v>
+        <v>46157.93150404634</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93150404634</v>
+        <v>46157.93392790922</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93392790922</v>
+        <v>46157.93706584216</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93706584216</v>
+        <v>46158.28209898892</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28209898892</v>
+        <v>46158.29664629214</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29664629214</v>
+        <v>46158.29803344245</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29803344245</v>
+        <v>46158.33380524119</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33380524119</v>
+        <v>46158.36846649298</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36846649298</v>
+        <v>46158.37280835187</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
